--- a/data/trans_orig/IP25A-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP25A-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>3957</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13533</t>
+          <t>13112</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1843</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8939</t>
+          <t>8573</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7105</t>
+          <t>6962</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18320</t>
+          <t>18421</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19718</t>
+          <t>19299</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>33559</t>
+          <t>33207</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,74%</t>
+          <t>39,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17926</t>
+          <t>18119</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30881</t>
+          <t>30865</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>41273</t>
+          <t>41337</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60513</t>
+          <t>60735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,67%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>34351</t>
+          <t>35384</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>48970</t>
+          <t>49895</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,9%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33488</t>
+          <t>33203</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>46953</t>
+          <t>47249</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>43,6%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>61,14%</t>
+          <t>61,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>72295</t>
+          <t>71916</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>92045</t>
+          <t>92691</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>57,08%</t>
+          <t>57,48%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4707</t>
+          <t>4804</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>14088</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,05%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4772</t>
+          <t>4183</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>13513</t>
+          <t>13224</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11389</t>
+          <t>12074</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23921</t>
+          <t>24720</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,33%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21575</t>
+          <t>21057</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38451</t>
+          <t>38116</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>31715</t>
+          <t>31618</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>50097</t>
+          <t>50122</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>57048</t>
+          <t>56996</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>83594</t>
+          <t>82689</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,31%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>110154</t>
+          <t>109888</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>140233</t>
+          <t>140708</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>37,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>115656</t>
+          <t>115345</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>146369</t>
+          <t>144415</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>233432</t>
+          <t>234208</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>276228</t>
+          <t>275310</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>34,32%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>158324</t>
+          <t>156563</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>191233</t>
+          <t>188653</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>180022</t>
+          <t>179399</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>212586</t>
+          <t>211718</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>50,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>346350</t>
+          <t>348803</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>392080</t>
+          <t>392675</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>43,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,95%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>42077</t>
+          <t>42464</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>63213</t>
+          <t>64728</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46500</t>
+          <t>46744</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>68354</t>
+          <t>70407</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>94578</t>
+          <t>94815</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124508</t>
+          <t>125630</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,66%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>730</t>
+          <t>740</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9518</t>
+          <t>9353</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4012</t>
+          <t>4129</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13035</t>
+          <t>12671</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25535</t>
+          <t>24687</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>41806</t>
+          <t>41323</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30122</t>
+          <t>30391</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>45846</t>
+          <t>46745</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,19%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>34,98%</t>
+          <t>35,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>59441</t>
+          <t>59094</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>83804</t>
+          <t>82130</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,17%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80084</t>
+          <t>80175</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>98993</t>
+          <t>100066</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>66,51%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>57956</t>
+          <t>56768</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>75667</t>
+          <t>75077</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>141181</t>
+          <t>142351</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>169361</t>
+          <t>168096</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>59,71%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18105</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>32864</t>
+          <t>33875</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15873</t>
+          <t>15651</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29452</t>
+          <t>29110</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>22,47%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36759</t>
+          <t>38061</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57390</t>
+          <t>58462</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,77%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>29970</t>
+          <t>30592</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50301</t>
+          <t>51218</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39219</t>
+          <t>39628</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60654</t>
+          <t>60148</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>73637</t>
+          <t>74053</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103753</t>
+          <t>104802</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>166951</t>
+          <t>164920</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>202876</t>
+          <t>201864</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>27,2%</t>
+          <t>26,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>33,06%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>175270</t>
+          <t>172998</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>209729</t>
+          <t>209656</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>349745</t>
+          <t>346953</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>402122</t>
+          <t>399778</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>27,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,11%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>282798</t>
+          <t>285411</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>324170</t>
+          <t>324598</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>52,89%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>283459</t>
+          <t>282502</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>321861</t>
+          <t>321667</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>579507</t>
+          <t>581467</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>641504</t>
+          <t>638310</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>51,27%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>72235</t>
+          <t>73778</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>99891</t>
+          <t>101906</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>74182</t>
+          <t>73795</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>102204</t>
+          <t>101836</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>154116</t>
+          <t>152997</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>190961</t>
+          <t>191982</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,42%</t>
         </is>
       </c>
     </row>
@@ -3240,12 +3240,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3458</t>
+          <t>3449</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11728</t>
+          <t>11911</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3255,12 +3255,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>3959</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12136</t>
+          <t>12359</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3290,12 +3290,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3310,12 +3310,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9492</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20999</t>
+          <t>21315</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3325,12 +3325,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,68%</t>
         </is>
       </c>
     </row>
@@ -3353,12 +3353,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23555</t>
+          <t>23883</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38550</t>
+          <t>38418</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3368,12 +3368,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>44,47%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20213</t>
+          <t>20245</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34794</t>
+          <t>34258</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3423,12 +3423,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>47856</t>
+          <t>47630</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68424</t>
+          <t>67663</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>40,25%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26570</t>
+          <t>26413</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41756</t>
+          <t>41217</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>47,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>29761</t>
+          <t>29277</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>45007</t>
+          <t>44836</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>35,95%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60140</t>
+          <t>59352</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>81764</t>
+          <t>80959</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>48,16%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10390</t>
+          <t>10351</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22216</t>
+          <t>21556</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>5941</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15757</t>
+          <t>16568</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18696</t>
+          <t>18655</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34216</t>
+          <t>33725</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -3809,12 +3809,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>20904</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>37930</t>
+          <t>38522</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3824,12 +3824,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3844,12 +3844,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>32875</t>
+          <t>32419</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>53865</t>
+          <t>52526</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3879,12 +3879,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>58666</t>
+          <t>60184</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>87008</t>
+          <t>84471</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3922,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>99743</t>
+          <t>101014</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>129899</t>
+          <t>130300</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3937,12 +3937,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,17%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3957,12 +3957,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109829</t>
+          <t>110994</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>140358</t>
+          <t>141521</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3972,12 +3972,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3992,12 +3992,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>218000</t>
+          <t>216480</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>260973</t>
+          <t>260960</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4007,12 +4007,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>25,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -4035,12 +4035,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>172691</t>
+          <t>173810</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>204958</t>
+          <t>206676</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4050,12 +4050,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>52,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>204878</t>
+          <t>206205</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>239760</t>
+          <t>240222</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>45,52%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>391505</t>
+          <t>391310</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>438904</t>
+          <t>438526</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4120,12 +4120,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>51,86%</t>
+          <t>51,82%</t>
         </is>
       </c>
     </row>
@@ -4148,12 +4148,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50945</t>
+          <t>51148</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>75718</t>
+          <t>73995</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4163,12 +4163,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>47095</t>
+          <t>46360</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>72285</t>
+          <t>71968</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4198,12 +4198,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>104789</t>
+          <t>105395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>139279</t>
+          <t>137737</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4233,12 +4233,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>16,46%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -4378,12 +4378,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7303</t>
+          <t>7017</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18898</t>
+          <t>18366</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4393,12 +4393,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6355</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18204</t>
+          <t>17763</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4428,12 +4428,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15700</t>
+          <t>15653</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>32455</t>
+          <t>31865</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4463,12 +4463,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -4491,12 +4491,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23381</t>
+          <t>23059</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40096</t>
+          <t>40491</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,47%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26867</t>
+          <t>26980</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>44511</t>
+          <t>44393</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4541,12 +4541,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>54584</t>
+          <t>55067</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>79198</t>
+          <t>80139</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -4576,12 +4576,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,72%</t>
         </is>
       </c>
     </row>
@@ -4604,12 +4604,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69008</t>
+          <t>69071</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89901</t>
+          <t>89582</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,3%</t>
+          <t>46,34%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>60,31%</t>
+          <t>60,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>70920</t>
+          <t>72048</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92160</t>
+          <t>91829</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4654,12 +4654,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>146964</t>
+          <t>145461</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175586</t>
+          <t>175648</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4689,12 +4689,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,56%</t>
         </is>
       </c>
     </row>
@@ -4717,12 +4717,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19407</t>
+          <t>19665</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>33966</t>
+          <t>35577</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4732,12 +4732,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15886</t>
+          <t>16393</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31284</t>
+          <t>31915</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4767,12 +4767,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>40030</t>
+          <t>39289</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61397</t>
+          <t>61749</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4802,12 +4802,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>20,47%</t>
+          <t>20,59%</t>
         </is>
       </c>
     </row>
@@ -4947,12 +4947,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>37854</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59229</t>
+          <t>60591</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -4962,12 +4962,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>48903</t>
+          <t>50315</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>73449</t>
+          <t>76943</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>93758</t>
+          <t>92630</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>126628</t>
+          <t>124527</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5032,12 +5032,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,47%</t>
         </is>
       </c>
     </row>
@@ -5060,12 +5060,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>157589</t>
+          <t>158906</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>197938</t>
+          <t>195581</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5075,12 +5075,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>168132</t>
+          <t>169411</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>206813</t>
+          <t>208390</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5110,12 +5110,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,54%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>335403</t>
+          <t>338591</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>388618</t>
+          <t>392366</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,85%</t>
         </is>
       </c>
     </row>
@@ -5173,12 +5173,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>282950</t>
+          <t>282209</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>324299</t>
+          <t>323836</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5208,12 +5208,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>319854</t>
+          <t>319569</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>363535</t>
+          <t>361574</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5223,12 +5223,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>46,87%</t>
+          <t>46,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>53,27%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>614815</t>
+          <t>615175</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>674486</t>
+          <t>675431</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5258,12 +5258,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,39%</t>
         </is>
       </c>
     </row>
@@ -5286,12 +5286,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>89794</t>
+          <t>89695</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>118900</t>
+          <t>120209</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5321,12 +5321,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>78432</t>
+          <t>77138</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>107776</t>
+          <t>108255</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5336,12 +5336,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5356,12 +5356,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>177331</t>
+          <t>173503</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>220223</t>
+          <t>216764</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5371,12 +5371,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -5747,12 +5747,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6999</t>
+          <t>7045</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17112</t>
+          <t>17194</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5762,12 +5762,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5782,12 +5782,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4092</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12519</t>
+          <t>12666</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5797,12 +5797,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,61%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5817,12 +5817,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12977</t>
+          <t>12849</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>26601</t>
+          <t>25918</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5832,12 +5832,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>22,51%</t>
         </is>
       </c>
     </row>
@@ -5860,12 +5860,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9994</t>
+          <t>10187</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20711</t>
+          <t>21096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5875,12 +5875,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,38%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5895,12 +5895,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20115</t>
+          <t>19978</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32817</t>
+          <t>33642</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5910,12 +5910,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5930,12 +5930,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32991</t>
+          <t>33488</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>50462</t>
+          <t>49830</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5945,12 +5945,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,66%</t>
+          <t>29,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>43,83%</t>
+          <t>43,28%</t>
         </is>
       </c>
     </row>
@@ -5973,12 +5973,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15026</t>
+          <t>15133</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26613</t>
+          <t>26664</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5988,12 +5988,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6008,12 +6008,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>16225</t>
+          <t>16290</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29803</t>
+          <t>28988</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6023,12 +6023,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35399</t>
+          <t>35410</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>52460</t>
+          <t>52207</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6058,12 +6058,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>30,75%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,35%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>8214</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3513</t>
+          <t>3522</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12473</t>
+          <t>11571</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>7047</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17886</t>
+          <t>17528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -6316,12 +6316,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39824</t>
+          <t>39859</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>61518</t>
+          <t>62256</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6331,12 +6331,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6351,12 +6351,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43349</t>
+          <t>43050</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66526</t>
+          <t>66077</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6366,12 +6366,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6386,12 +6386,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>87780</t>
+          <t>87295</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>120956</t>
+          <t>120499</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,81%</t>
         </is>
       </c>
     </row>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>140096</t>
+          <t>142342</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>173123</t>
+          <t>173063</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6464,12 +6464,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>140758</t>
+          <t>142086</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>173875</t>
+          <t>177189</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6499,12 +6499,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>292649</t>
+          <t>289595</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>338367</t>
+          <t>337222</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6514,12 +6514,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,66%</t>
         </is>
       </c>
     </row>
@@ -6542,12 +6542,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>143814</t>
+          <t>145399</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>177525</t>
+          <t>175572</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6557,12 +6557,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>172118</t>
+          <t>171453</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>207005</t>
+          <t>206969</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6592,12 +6592,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,08%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6612,12 +6612,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>327531</t>
+          <t>326333</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>374866</t>
+          <t>376146</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6627,12 +6627,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>43,12%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>46401</t>
+          <t>46136</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>68845</t>
+          <t>68904</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,29%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>37028</t>
+          <t>37158</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>58502</t>
+          <t>58634</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>89986</t>
+          <t>90368</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>120674</t>
+          <t>122295</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>14,02%</t>
         </is>
       </c>
     </row>
@@ -6885,12 +6885,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5573</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>16655</t>
+          <t>16681</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6920,12 +6920,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5565</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16604</t>
+          <t>17081</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6935,12 +6935,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,25%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6955,12 +6955,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>12737</t>
+          <t>13524</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27910</t>
+          <t>28757</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6970,12 +6970,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -6998,12 +6998,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>28877</t>
+          <t>29144</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46429</t>
+          <t>47001</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7013,12 +7013,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -7033,12 +7033,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>41278</t>
+          <t>40979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61132</t>
+          <t>61493</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,48%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>75618</t>
+          <t>75217</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>100214</t>
+          <t>102099</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,26%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>32,93%</t>
         </is>
       </c>
     </row>
@@ -7111,12 +7111,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>61495</t>
+          <t>62706</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>82247</t>
+          <t>82780</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7126,12 +7126,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61278</t>
+          <t>61401</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>82222</t>
+          <t>81578</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>129426</t>
+          <t>128461</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>157150</t>
+          <t>158089</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,69%</t>
+          <t>50,99%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21906</t>
+          <t>21418</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38142</t>
+          <t>37465</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22217</t>
+          <t>21919</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>37742</t>
+          <t>37677</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>48032</t>
+          <t>47032</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70478</t>
+          <t>70369</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -7454,12 +7454,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>58695</t>
+          <t>58241</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>85717</t>
+          <t>85247</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7469,12 +7469,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7489,12 +7489,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>59086</t>
+          <t>58603</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>86155</t>
+          <t>86721</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>123066</t>
+          <t>124589</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>162683</t>
+          <t>160649</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,38%</t>
         </is>
       </c>
     </row>
@@ -7567,12 +7567,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>188833</t>
+          <t>191259</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>227249</t>
+          <t>228033</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7582,12 +7582,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,64%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7602,12 +7602,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>215024</t>
+          <t>215317</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>254255</t>
+          <t>256362</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7617,12 +7617,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7637,12 +7637,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>414361</t>
+          <t>417968</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>471036</t>
+          <t>472738</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7652,12 +7652,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>31,94%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>36,44%</t>
         </is>
       </c>
     </row>
@@ -7680,12 +7680,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>233220</t>
+          <t>233266</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>272039</t>
+          <t>272241</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7695,12 +7695,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7715,12 +7715,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>263962</t>
+          <t>262142</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>305403</t>
+          <t>305591</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>39,1%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7750,12 +7750,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>509038</t>
+          <t>507451</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>566359</t>
+          <t>564289</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7765,12 +7765,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>39,11%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>43,49%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>77686</t>
+          <t>77355</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>106354</t>
+          <t>104903</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>70086</t>
+          <t>70337</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>98611</t>
+          <t>97781</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>153922</t>
+          <t>154429</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>194687</t>
+          <t>194649</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,0%</t>
         </is>
       </c>
     </row>
@@ -8259,7 +8259,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3276</t>
+          <t>2955</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8289,12 +8289,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>529</t>
+          <t>520</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6810</t>
+          <t>6783</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8324,12 +8324,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>840</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>7409</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -8367,12 +8367,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19252</t>
+          <t>20646</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8382,12 +8382,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>9,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8402,12 +8402,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17204</t>
+          <t>16521</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>26,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8437,12 +8437,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12611</t>
+          <t>13145</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>30076</t>
+          <t>31758</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>28,24%</t>
         </is>
       </c>
     </row>
@@ -8480,12 +8480,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20534</t>
+          <t>19681</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>36873</t>
+          <t>36169</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8495,12 +8495,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8515,12 +8515,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25701</t>
+          <t>26559</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>39924</t>
+          <t>39583</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,99%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8550,12 +8550,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>50952</t>
+          <t>50509</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>73167</t>
+          <t>73178</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>45,31%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,08%</t>
         </is>
       </c>
     </row>
@@ -8593,12 +8593,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7122</t>
+          <t>7015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18595</t>
+          <t>18475</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8608,12 +8608,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8628,12 +8628,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9207</t>
+          <t>10199</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20672</t>
+          <t>21678</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8663,12 +8663,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>20260</t>
+          <t>19488</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>37049</t>
+          <t>35846</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8678,12 +8678,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>31,88%</t>
         </is>
       </c>
     </row>
@@ -8823,12 +8823,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9154</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>27837</t>
+          <t>27216</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8838,12 +8838,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8858,12 +8858,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4663</t>
+          <t>4704</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15917</t>
+          <t>16293</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8893,12 +8893,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>16295</t>
+          <t>17193</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37577</t>
+          <t>39821</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -8936,12 +8936,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>33207</t>
+          <t>32843</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55900</t>
+          <t>55909</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8951,7 +8951,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -8971,12 +8971,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46722</t>
+          <t>44877</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72908</t>
+          <t>71738</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9006,12 +9006,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83805</t>
+          <t>84603</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120784</t>
+          <t>120862</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9021,7 +9021,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -9049,12 +9049,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>165217</t>
+          <t>161072</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>225361</t>
+          <t>226028</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9064,12 +9064,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,72%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9084,12 +9084,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>214516</t>
+          <t>213754</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>263944</t>
+          <t>261222</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,73%</t>
+          <t>41,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9119,12 +9119,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>404446</t>
+          <t>397906</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>477692</t>
+          <t>476415</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9134,12 +9134,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,25%</t>
         </is>
       </c>
     </row>
@@ -9162,12 +9162,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>166491</t>
+          <t>167717</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>247197</t>
+          <t>244539</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>36,73%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>53,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9197,12 +9197,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183865</t>
+          <t>183950</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>237429</t>
+          <t>234116</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9212,12 +9212,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>362484</t>
+          <t>362240</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>452298</t>
+          <t>452534</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9247,12 +9247,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,78%</t>
         </is>
       </c>
     </row>
@@ -9392,12 +9392,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>848</t>
+          <t>832</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8250</t>
+          <t>7693</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9407,12 +9407,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9427,12 +9427,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1158</t>
+          <t>953</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10130</t>
+          <t>10327</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9462,12 +9462,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3016</t>
+          <t>3530</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14110</t>
+          <t>13793</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -9505,12 +9505,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11582</t>
+          <t>11325</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>24713</t>
+          <t>24802</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9520,12 +9520,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -9540,12 +9540,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12229</t>
+          <t>12123</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29530</t>
+          <t>28962</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9555,12 +9555,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>27012</t>
+          <t>27070</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>47292</t>
+          <t>48292</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9590,12 +9590,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,55%</t>
         </is>
       </c>
     </row>
@@ -9618,12 +9618,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>51533</t>
+          <t>50701</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>70940</t>
+          <t>70870</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9633,12 +9633,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,71%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9653,12 +9653,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>74996</t>
+          <t>73392</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>98796</t>
+          <t>100012</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9668,12 +9668,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,88%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9688,12 +9688,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>132882</t>
+          <t>130279</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>163890</t>
+          <t>163627</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9703,12 +9703,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,26%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,31%</t>
         </is>
       </c>
     </row>
@@ -9731,12 +9731,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56875</t>
+          <t>58242</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76952</t>
+          <t>77199</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9746,12 +9746,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9766,12 +9766,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61693</t>
+          <t>61414</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>85999</t>
+          <t>86111</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9781,12 +9781,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>33,65%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9801,12 +9801,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>127011</t>
+          <t>124476</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>156832</t>
+          <t>158198</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9816,12 +9816,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>38,28%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>47,26%</t>
+          <t>47,68%</t>
         </is>
       </c>
     </row>
@@ -9961,12 +9961,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12487</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32261</t>
+          <t>31466</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9976,12 +9976,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9996,12 +9996,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>9071</t>
+          <t>8997</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24585</t>
+          <t>23920</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10011,12 +10011,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10031,12 +10031,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24870</t>
+          <t>25624</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49050</t>
+          <t>48892</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10046,12 +10046,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
     </row>
@@ -10074,12 +10074,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56712</t>
+          <t>55840</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88067</t>
+          <t>86476</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10089,12 +10089,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10109,12 +10109,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>73126</t>
+          <t>73930</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>105371</t>
+          <t>106747</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10124,12 +10124,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10144,12 +10144,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>138732</t>
+          <t>139177</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>182854</t>
+          <t>184911</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10159,12 +10159,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,1%</t>
         </is>
       </c>
     </row>
@@ -10187,12 +10187,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>253466</t>
+          <t>255527</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>319169</t>
+          <t>320336</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10202,12 +10202,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>48,89%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10222,12 +10222,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>327451</t>
+          <t>327457</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>384438</t>
+          <t>385562</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10242,7 +10242,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>50,66%</t>
+          <t>50,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10257,12 +10257,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>603198</t>
+          <t>605247</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>688199</t>
+          <t>695185</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10272,12 +10272,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,25%</t>
         </is>
       </c>
     </row>
@@ -10300,12 +10300,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>242306</t>
+          <t>243163</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>321439</t>
+          <t>323575</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10315,12 +10315,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>37,12%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>270044</t>
+          <t>269488</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>326274</t>
+          <t>330181</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10350,12 +10350,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10370,12 +10370,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>526457</t>
+          <t>520320</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>620354</t>
+          <t>621324</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10385,12 +10385,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,3%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,95%</t>
+          <t>44,02%</t>
         </is>
       </c>
     </row>
